--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-23T01:59:17.367Z</t>
+    <t>2026-06-23T19:02:48.813Z</t>
   </si>
   <si>
     <t>Honeywell Technologies: Leading the Journey to Industrial Autonomy</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-23T19:02:48.813Z</t>
+    <t>2026-06-24T17:08:53.694Z</t>
   </si>
   <si>
     <t>Honeywell Technologies: Leading the Journey to Industrial Autonomy</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-24T17:08:53.694Z</t>
+    <t>2026-06-24T18:35:36.038Z</t>
   </si>
   <si>
     <t>Honeywell Technologies: Leading the Journey to Industrial Autonomy</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-24T18:35:36.038Z</t>
+    <t>2026-06-24T20:16:20.689Z</t>
   </si>
   <si>
     <t>Honeywell Technologies: Leading the Journey to Industrial Autonomy</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-24T20:16:20.689Z</t>
+    <t>2026-06-24T22:53:20.033Z</t>
   </si>
   <si>
     <t>Honeywell Technologies: Leading the Journey to Industrial Autonomy</t>
